--- a/test/tdsreturn.xlsx
+++ b/test/tdsreturn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C931BFB-9DB7-4ED5-B39F-192A3ED4EEAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF15EBD-3193-421B-8C32-77EEDE511E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{D99CBEC2-83A2-4352-8F4C-20C503A25BA4}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>TDS Section</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>192A - Premature withdrawal from EPF</t>
+  </si>
+  <si>
+    <t>78@@87</t>
   </si>
 </sst>
 </file>
@@ -492,8 +495,8 @@
       <c r="F2" s="1">
         <v>37591</v>
       </c>
-      <c r="G2">
-        <v>7887</v>
+      <c r="G2" t="s">
+        <v>13</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
